--- a/output/excel/pareto_metrics_real_sparse_r04_c40_u130_k10_s1.xlsx
+++ b/output/excel/pareto_metrics_real_sparse_r04_c40_u130_k10_s1.xlsx
@@ -465,19 +465,19 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>1.048108089751652</v>
+        <v>0.9417420290395031</v>
       </c>
       <c r="D2">
-        <v>0.01926677663461046</v>
+        <v>0.08446065768575214</v>
       </c>
       <c r="E2">
-        <v>0.01013173497384534</v>
+        <v>0.007919526897546561</v>
       </c>
       <c r="F2">
-        <v>0.234372854637608</v>
+        <v>0.3005755381403313</v>
       </c>
       <c r="G2">
-        <v>0.234372854637608</v>
+        <v>0.3005755381403313</v>
       </c>
       <c r="H2">
         <v>50</v>
@@ -486,10 +486,10 @@
         <v>50</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.04867449132419035</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.05076510713804888</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -500,19 +500,19 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>1.047780699234623</v>
+        <v>0.9821574525436092</v>
       </c>
       <c r="D3">
-        <v>0.02634962211921447</v>
+        <v>0.05420532320457871</v>
       </c>
       <c r="E3">
-        <v>0.008071084333436094</v>
+        <v>0.008557615369936211</v>
       </c>
       <c r="F3">
-        <v>0.2420890074343048</v>
+        <v>0.2686829660839594</v>
       </c>
       <c r="G3">
-        <v>0.2420890074343048</v>
+        <v>0.2686829660839594</v>
       </c>
       <c r="H3">
         <v>50</v>
@@ -521,10 +521,10 @@
         <v>50</v>
       </c>
       <c r="J3">
-        <v>0.01026475047852845</v>
+        <v>0.06587575054965319</v>
       </c>
       <c r="K3">
-        <v>0.004932609389277138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -535,19 +535,19 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>1.025227905552204</v>
+        <v>0.9766103438427645</v>
       </c>
       <c r="D4">
-        <v>0.04045527178708211</v>
+        <v>0.06425768260914257</v>
       </c>
       <c r="E4">
-        <v>0.004231543606490276</v>
+        <v>0.006110099537712618</v>
       </c>
       <c r="F4">
-        <v>0.2385479433660541</v>
+        <v>0.2674209257539141</v>
       </c>
       <c r="G4">
-        <v>0.2385479433660541</v>
+        <v>0.2674209257539141</v>
       </c>
       <c r="H4">
         <v>50</v>
@@ -556,10 +556,10 @@
         <v>50</v>
       </c>
       <c r="J4">
-        <v>0.05311243957116873</v>
+        <v>0.03626449434458748</v>
       </c>
       <c r="K4">
-        <v>0.02198094180334862</v>
+        <v>0.06868849006838798</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -570,19 +570,19 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>1.049016824830038</v>
+        <v>1.040842447089763</v>
       </c>
       <c r="D5">
-        <v>0.0192395051073223</v>
+        <v>0.009962818552146768</v>
       </c>
       <c r="E5">
-        <v>0.007492359123866299</v>
+        <v>0.006952865872091502</v>
       </c>
       <c r="F5">
-        <v>0.2273324743696142</v>
+        <v>0.2520656214859217</v>
       </c>
       <c r="G5">
-        <v>0.2273324743696142</v>
+        <v>0.2520656214859217</v>
       </c>
       <c r="H5">
         <v>50</v>
@@ -591,10 +591,10 @@
         <v>50</v>
       </c>
       <c r="J5">
-        <v>0.0005465201042215954</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.03663726056370952</v>
+        <v>0.01697945797035735</v>
       </c>
     </row>
   </sheetData>
